--- a/data/trans_orig/IP74A5_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP74A5_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto los impuestos.. en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos de los impuestos relacionados con vehículos, IBI, etc en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>70,73%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9337</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16804</t>
+          <t>16900</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11140</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,73%</t>
         </is>
       </c>
     </row>
